--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484672_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484672_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2378</v>
+        <v>10.7517</v>
       </c>
       <c r="E2" t="n">
-        <v>9.436999999999999</v>
+        <v>9.0253</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8007</v>
+        <v>1.7264</v>
       </c>
       <c r="G2" t="n">
         <v>1.6495</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9474</v>
+        <v>1.4613</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9027</v>
+        <v>1.491</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0447</v>
+        <v>-0.0296</v>
       </c>
       <c r="V2" t="n">
         <v>5.4417</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5611</v>
+        <v>3.971</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1773</v>
+        <v>4.4386</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6162</v>
+        <v>-0.4676</v>
       </c>
       <c r="G3" t="n">
         <v>1.5084</v>
@@ -688,13 +688,13 @@
         <v>2.9321</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7393999999999999</v>
+        <v>1.1493</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2436</v>
+        <v>1.5049</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5042</v>
+        <v>-0.3556</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5193</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1475</v>
+        <v>3.4006</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0446</v>
+        <v>1.2333</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1921</v>
+        <v>2.1673</v>
       </c>
       <c r="G4" t="n">
         <v>0.1775</v>
@@ -766,13 +766,13 @@
         <v>2.7489</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1259</v>
+        <v>1.1273</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5881999999999999</v>
+        <v>0.6897</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4623</v>
+        <v>0.4376</v>
       </c>
       <c r="V4" t="n">
         <v>0.4466</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9712</v>
+        <v>2.0298</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5891</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2177</v>
+        <v>1.4407</v>
       </c>
       <c r="G5" t="n">
         <v>0.4687</v>
@@ -844,13 +844,13 @@
         <v>2.9321</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1109</v>
+        <v>0.1695</v>
       </c>
       <c r="T5" t="n">
-        <v>0.675</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5641</v>
+        <v>-0.3411</v>
       </c>
       <c r="V5" t="n">
         <v>1.3916</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1902</v>
+        <v>0.36</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1973</v>
+        <v>-0.8949</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0071</v>
+        <v>1.2549</v>
       </c>
       <c r="G6" t="n">
         <v>0.6084000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6599</v>
+        <v>-0.1097</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4593</v>
+        <v>-0.1568</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2006</v>
+        <v>0.0471</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. POVEDA CASTELLO</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3306</v>
+        <v>-1.0206</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.1342</v>
+        <v>-1.7686</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8036</v>
+        <v>0.748</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3517</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.1754</v>
+        <v>1.0874</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8236</v>
+        <v>-1.981</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5834</v>
+        <v>0.5004</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.5677</v>
+        <v>2.8978</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9843</v>
+        <v>-2.3974</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7683</v>
+        <v>-1.394</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6077</v>
+        <v>-1.8104</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1606</v>
+        <v>0.4164</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.6651</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.5973</v>
+        <v>-2.7489</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9321</v>
+        <v>2.5656</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7503</v>
+        <v>0.9389</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2248</v>
+        <v>0.7809</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5256</v>
+        <v>0.158</v>
       </c>
       <c r="V7" t="n">
-        <v>3.9359</v>
+        <v>-0.8827</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8217</v>
+        <v>-0.3011</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1142</v>
+        <v>-0.5816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>M. POVEDA CASTELLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7546</v>
+        <v>-1.1009</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.453</v>
+        <v>-4.1613</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6985</v>
+        <v>3.0604</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-3.3517</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0874</v>
+        <v>-4.1754</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.981</v>
+        <v>0.8236</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5004</v>
+        <v>-2.5834</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8978</v>
+        <v>-3.5677</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.3974</v>
+        <v>0.9843</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.394</v>
+        <v>-0.7683</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8104</v>
+        <v>-0.6077</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4164</v>
+        <v>-0.1606</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1833</v>
+        <v>-3.6651</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7489</v>
+        <v>-6.5973</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5656</v>
+        <v>2.9321</v>
       </c>
       <c r="S8" t="n">
-        <v>1.205</v>
+        <v>1.98</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0966</v>
+        <v>1.1976</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1084</v>
+        <v>0.7824</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8827</v>
+        <v>3.9359</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3011</v>
+        <v>3.8217</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5816</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.079499999999999</v>
+        <v>-7.4525</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.6675</v>
+        <v>-6.2139</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.412</v>
+        <v>-1.2386</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7909</v>
@@ -1156,13 +1156,13 @@
         <v>2.5656</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2886</v>
+        <v>0.3384</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4744</v>
+        <v>0.928</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.763</v>
+        <v>-0.5896</v>
       </c>
       <c r="V9" t="n">
         <v>-1.9005</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.562700000000001</v>
+        <v>10.9391</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8712</v>
+        <v>2.2476</v>
       </c>
       <c r="F10" t="n">
         <v>8.6915</v>
@@ -1234,13 +1234,13 @@
         <v>20.1582</v>
       </c>
       <c r="S10" t="n">
-        <v>5.678599999999999</v>
+        <v>7.055</v>
       </c>
       <c r="T10" t="n">
-        <v>5.5696</v>
+        <v>6.945899999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1091000000000001</v>
+        <v>0.1091999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>7.5914</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.6037</v>
+        <v>2.3677</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5039</v>
+        <v>1.7346</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0998</v>
+        <v>0.6331</v>
       </c>
       <c r="G11" t="n">
         <v>1.57</v>
@@ -1312,13 +1312,13 @@
         <v>3.2986</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2997</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5362</v>
+        <v>0.767</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2365</v>
+        <v>-0.7033</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3655</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5022</v>
+        <v>0.2777</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5476</v>
+        <v>-1.7399</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0497</v>
+        <v>2.0175</v>
       </c>
       <c r="G13" t="n">
         <v>1.3312</v>
@@ -1468,13 +1468,13 @@
         <v>3.6651</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0866</v>
+        <v>-0.3111</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3997</v>
+        <v>0.2074</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4863</v>
+        <v>-0.5185</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3759</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3389</v>
+        <v>0.1735</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3363</v>
+        <v>-0.384</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9974</v>
+        <v>0.5575</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9129</v>
+        <v>1.4048</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0446</v>
+        <v>1.5334</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1317</v>
+        <v>-0.1285</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3883</v>
+        <v>1.9872</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2633</v>
+        <v>0.5445</v>
       </c>
       <c r="L14" t="n">
-        <v>0.125</v>
+        <v>1.4427</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5246</v>
+        <v>-0.5824</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7813</v>
+        <v>0.9888</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2567</v>
+        <v>-1.5712</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0995</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9321</v>
+        <v>-4.0317</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8326</v>
+        <v>3.4819</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4364</v>
+        <v>-0.6276</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2911</v>
+        <v>0.0611</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1453</v>
+        <v>-0.6888</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9109</v>
+        <v>-0.054</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5889</v>
+        <v>1.5993</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.4998</v>
+        <v>-1.6533</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6065</v>
+        <v>-0.3822</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6837</v>
+        <v>-0.5876</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0772</v>
+        <v>0.2054</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1119</v>
@@ -1624,13 +1624,13 @@
         <v>0.1833</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2014</v>
+        <v>0.023</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U15" t="n">
-        <v>0.129</v>
+        <v>0.2572</v>
       </c>
       <c r="V15" t="n">
         <v>0.6231</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7255</v>
+        <v>-0.3941</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5763</v>
+        <v>1.144</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1492</v>
+        <v>-1.538</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4048</v>
+        <v>2.9129</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5334</v>
+        <v>3.0446</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1285</v>
+        <v>-0.1317</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9872</v>
+        <v>2.3883</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5445</v>
+        <v>2.2633</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4427</v>
+        <v>0.125</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5824</v>
+        <v>0.5246</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9888</v>
+        <v>0.7813</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5712</v>
+        <v>-0.2567</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5498</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0317</v>
+        <v>-2.9321</v>
       </c>
       <c r="R16" t="n">
-        <v>3.4819</v>
+        <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5266</v>
+        <v>-0.2966</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1312</v>
+        <v>0.0988</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3954</v>
+        <v>-0.3954</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.054</v>
+        <v>-1.9109</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5993</v>
+        <v>1.5889</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6533</v>
+        <v>-3.4998</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3145</v>
+        <v>-0.6676</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6427</v>
+        <v>-0.4503</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6718</v>
+        <v>-0.2172</v>
       </c>
       <c r="G17" t="n">
         <v>0.4622</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4259</v>
+        <v>-0.779</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5784</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6552</v>
+        <v>-0.2006</v>
       </c>
       <c r="V17" t="n">
         <v>-1.267</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.922</v>
+        <v>-0.7564</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.0595</v>
+        <v>-3.6749</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1375</v>
+        <v>2.9185</v>
       </c>
       <c r="G18" t="n">
         <v>-1.134</v>
@@ -1858,13 +1858,13 @@
         <v>2.9321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5691</v>
+        <v>-0.4035</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6621</v>
+        <v>-0.2775</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.907</v>
+        <v>-0.126</v>
       </c>
       <c r="V18" t="n">
         <v>1.5141</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5331</v>
+        <v>-3.3802</v>
       </c>
       <c r="E19" t="n">
         <v>-2.0492</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4839</v>
+        <v>-1.331</v>
       </c>
       <c r="G19" t="n">
         <v>0.246</v>
@@ -1936,13 +1936,13 @@
         <v>0.1833</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6796</v>
+        <v>-0.5266</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.4715</v>
       </c>
       <c r="V19" t="n">
         <v>-1.267</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5561</v>
+        <v>-4.8874</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6228</v>
+        <v>-3.3344</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9333</v>
+        <v>-1.553</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7076</v>
@@ -2014,13 +2014,13 @@
         <v>2.7489</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9257</v>
+        <v>-0.257</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3869</v>
+        <v>-0.0984</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5389</v>
+        <v>-0.1586</v>
       </c>
       <c r="V20" t="n">
         <v>-4.4884</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.5627</v>
+        <v>-6.9988</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.6914</v>
+        <v>-8.691500000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8713999999999993</v>
+        <v>1.6928</v>
       </c>
       <c r="G21" t="n">
         <v>4.623800000000001</v>
@@ -2065,7 +2065,7 @@
         <v>-7.6938</v>
       </c>
       <c r="J21" t="n">
-        <v>8.024099999999999</v>
+        <v>8.024100000000001</v>
       </c>
       <c r="K21" t="n">
         <v>9.1441</v>
@@ -2092,19 +2092,19 @@
         <v>19.2421</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.6788</v>
+        <v>-3.1147</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1092999999999998</v>
+        <v>-0.1093</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.5695</v>
+        <v>-3.0055</v>
       </c>
       <c r="V21" t="n">
         <v>-7.5915</v>
       </c>
       <c r="W21" t="n">
-        <v>3.5518</v>
+        <v>3.551799999999999</v>
       </c>
       <c r="X21" t="n">
         <v>-11.1433</v>
